--- a/output/pdf_financials_xlsx/OMGA.xlsx
+++ b/output/pdf_financials_xlsx/OMGA.xlsx
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.011118</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.240664</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.19892</v>
       </c>
     </row>
     <row r="104">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.000243</v>
+        <v>0.011361</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.508564</v>
+        <v>0.2679</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.025242</v>
+        <v>0.173678</v>
       </c>
     </row>
     <row r="107">
@@ -2798,7 +2798,11 @@
           <t>Prepaids and deposit (note 3)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.00075</v>
       </c>
@@ -3271,7 +3275,11 @@
           <t>Warrant reserves</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3606,7 +3614,11 @@
           <t>Prepaids and deposit</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -4110,7 +4122,11 @@
           <t>Prepaids and deposit</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.011118</v>
       </c>

--- a/output/pdf_financials_xlsx/OMGA.xlsx
+++ b/output/pdf_financials_xlsx/OMGA.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000604</v>
       </c>
     </row>
     <row r="13">
@@ -869,7 +869,7 @@
         <v>-3.499915</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.71898</v>
+        <v>-0.719584</v>
       </c>
     </row>
     <row r="28">
@@ -901,7 +901,7 @@
         <v>-3.499915</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.71898</v>
+        <v>-0.719584</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.348205</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.135342</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.380553</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.348205</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.135342</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.380553</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.349786</v>
+        <v>0.001581</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.510287</v>
+        <v>0.374945</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.455449</v>
+        <v>0.074896</v>
       </c>
     </row>
     <row r="49">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">

--- a/output/pdf_financials_xlsx/OMGA.xlsx
+++ b/output/pdf_financials_xlsx/OMGA.xlsx
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.02143</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.043261</v>
       </c>
     </row>
     <row r="68">
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.017459</v>
       </c>
     </row>
     <row r="111">
@@ -3490,7 +3490,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
